--- a/Run/DataBundles/테이블/경기스킬_6종.xlsx
+++ b/Run/DataBundles/테이블/경기스킬_6종.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="경기스킬" sheetId="1" r:id="R18ea828888a646cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="경기스킬" sheetId="1" r:id="R93271a17861f49f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,8 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0%"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
+    <x:numFmt numFmtId="202" formatCode="0.0%"/>
+    <x:numFmt numFmtId="203" formatCode="0.0"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -73,7 +76,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -83,6 +86,9 @@
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -296,6 +302,12 @@
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -318,10 +330,10 @@
         <x:v>유니크</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>노말 시작률</x:v>
+        <x:v>노말 횟수</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>레어 시작률</x:v>
+        <x:v>레어 최소횟수</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
         <x:v>유니크 시작률</x:v>
@@ -331,6 +343,24 @@
       </x:c>
       <x:c r="K1" s="3" t="str">
         <x:v>지속(초)</x:v>
+      </x:c>
+      <x:c r="L1" s="3" t="str">
+        <x:v>레어 최대횟수</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="str">
+        <x:v>노말 속도율</x:v>
+      </x:c>
+      <x:c r="N1" s="3" t="str">
+        <x:v>노말 지속(초)</x:v>
+      </x:c>
+      <x:c r="O1" s="3" t="str">
+        <x:v>레어 속도율</x:v>
+      </x:c>
+      <x:c r="P1" s="3" t="str">
+        <x:v>레어 지속(초)</x:v>
+      </x:c>
+      <x:c r="Q1" s="3" t="str">
+        <x:v>레어 진로</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
@@ -352,20 +382,38 @@
       <x:c r="F2" s="6" t="str">
         <x:v>울지 마, 포링!</x:v>
       </x:c>
-      <x:c r="G2" s="7" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="H2" s="7" t="n">
-        <x:v>0.25</x:v>
+      <x:c r="G2" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H2" s="9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I2" s="7" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="J2" s="7" t="n">
         <x:v>0.11</x:v>
       </x:c>
       <x:c r="K2" s="1" t="n">
         <x:v>9</x:v>
+      </x:c>
+      <x:c r="L2" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M2" s="10" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="N2" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O2" s="10" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="P2" s="11" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="Q2" s="1" t="str">
+        <x:v>중앙</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
@@ -387,14 +435,14 @@
       <x:c r="F3" s="6" t="str">
         <x:v>대열 돌파</x:v>
       </x:c>
-      <x:c r="G3" s="7" t="n">
-        <x:v>0.12</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="n">
-        <x:v>0.28</x:v>
+      <x:c r="G3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H3" s="9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="7" t="n">
-        <x:v>0.63</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="J3" s="7" t="n">
         <x:v>0.15</x:v>
@@ -402,6 +450,24 @@
       <x:c r="K3" s="1" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="L3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M3" s="10" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="N3" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O3" s="10" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="P3" s="11" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="Q3" s="1" t="str">
+        <x:v>중앙</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="1" t="n">
@@ -422,20 +488,38 @@
       <x:c r="F4" s="6" t="str">
         <x:v>질주 본능</x:v>
       </x:c>
-      <x:c r="G4" s="7" t="n">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="H4" s="7" t="n">
-        <x:v>0.31</x:v>
+      <x:c r="G4" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H4" s="9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="7" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.76</x:v>
       </x:c>
       <x:c r="J4" s="7" t="n">
-        <x:v>0.17</x:v>
+        <x:v>0.34</x:v>
       </x:c>
       <x:c r="K4" s="1" t="n">
-        <x:v>7</x:v>
+        <x:v>13.5</x:v>
+      </x:c>
+      <x:c r="L4" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="N4" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O4" s="10" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="P4" s="11" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="Q4" s="1" t="str">
+        <x:v>외곽</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -457,20 +541,38 @@
       <x:c r="F5" s="6" t="str">
         <x:v>만월의 도약</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="n">
-        <x:v>0.16</x:v>
-      </x:c>
-      <x:c r="H5" s="7" t="n">
-        <x:v>0.34</x:v>
+      <x:c r="G5" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H5" s="9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="7" t="n">
-        <x:v>0.67</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="J5" s="7" t="n">
         <x:v>0.18</x:v>
       </x:c>
       <x:c r="K5" s="1" t="n">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="L5" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="N5" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O5" s="10" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="P5" s="11" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="Q5" s="1" t="str">
+        <x:v>외곽</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -492,20 +594,38 @@
       <x:c r="F6" s="6" t="str">
         <x:v>작은 마왕의 진격</x:v>
       </x:c>
-      <x:c r="G6" s="7" t="n">
-        <x:v>0.18</x:v>
-      </x:c>
-      <x:c r="H6" s="7" t="n">
-        <x:v>0.37</x:v>
+      <x:c r="G6" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H6" s="9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="7" t="n">
-        <x:v>0.69</x:v>
+        <x:v>0.52</x:v>
       </x:c>
       <x:c r="J6" s="7" t="n">
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="K6" s="1" t="n">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="L6" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M6" s="10" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="N6" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O6" s="10" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="P6" s="11" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="Q6" s="1" t="str">
+        <x:v>외곽</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
@@ -527,20 +647,38 @@
       <x:c r="F7" s="6" t="str">
         <x:v>구름길의 기적</x:v>
       </x:c>
-      <x:c r="G7" s="7" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="H7" s="7" t="n">
-        <x:v>0.4</x:v>
+      <x:c r="G7" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H7" s="9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="7" t="n">
-        <x:v>0.71</x:v>
+        <x:v>0.27</x:v>
       </x:c>
       <x:c r="J7" s="7" t="n">
         <x:v>0.16</x:v>
       </x:c>
       <x:c r="K7" s="1" t="n">
         <x:v>9</x:v>
+      </x:c>
+      <x:c r="L7" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="N7" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O7" s="10" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="P7" s="11" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="Q7" s="1" t="str">
+        <x:v>중앙</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -561,17 +699,17 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>노말 3회(시작률 + 0.28씩), 레어 2회(시작률 + 0.36), 유니크 1회. 노말·레어는 UI만 표시.</x:v>
+        <x:v>노말 2회, 레어 1~2회 랜덤. 경기 시작 때 순서를 추첨하고 전체 발동 사이 1.6초 이상 간격을 둔다.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>선택 캐릭터의 유니크는 60% 이후 1회 영상. 역전 보정은 유니크 발동 이후 후반 가속에만 적용.</x:v>
+        <x:v>유니크는 종별 초·중·후반에 1회. 선택 주자 영상도 종별 시점에 재생하며 이펙트는 영상 복귀 후 시작한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>힐·파워 업·다크 스트라이크는 라그나로크 스킬명 참고. 종별 배정·나머지 이름·효과는 데모용 창작.</x:v>
+        <x:v>노말은 미세 가속, 레어는 미세 가속과 진로 확보. 페코페코는 후반 외곽 추월과 강하고 긴 스퍼트를 사용한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
